--- a/output/pdf_financials_xlsx/ARS.xlsx
+++ b/output/pdf_financials_xlsx/ARS.xlsx
@@ -612,10 +612,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.186347</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.066718</v>
       </c>
     </row>
     <row r="13">
@@ -864,10 +864,10 @@
         <v>-4.437914</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.925347</v>
+        <v>-3.111694</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.641111</v>
+        <v>-3.707829</v>
       </c>
     </row>
     <row r="28">
@@ -896,10 +896,10 @@
         <v>-4.396799</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.885446</v>
+        <v>-3.071793</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.641111</v>
+        <v>-3.707829</v>
       </c>
     </row>
     <row r="30">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">

--- a/output/pdf_financials_xlsx/ARS.xlsx
+++ b/output/pdf_financials_xlsx/ARS.xlsx
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.407233</v>
       </c>
     </row>
     <row r="112">
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.521733</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.219548</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.407233</v>
       </c>
     </row>
     <row r="135">
@@ -2625,7 +2625,7 @@
         <v>0.427644</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.727882</v>
+        <v>-2.135115</v>
       </c>
     </row>
   </sheetData>
@@ -4611,7 +4611,11 @@
           <t>Purchase of equipment (10)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -4915,7 +4919,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -4944,7 +4952,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -5649,7 +5661,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E98" s="5" t="n">
         <v>0.521733</v>
       </c>
